--- a/events/OklahomaCity_2014_MAR/OklahomaCity_2014_MAR_Results.xlsx
+++ b/events/OklahomaCity_2014_MAR/OklahomaCity_2014_MAR_Results.xlsx
@@ -604,6 +604,11 @@
           <t>01:36:57.876</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1527,6 +1532,11 @@
           <t>01:44:10.282</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>98873</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3330,6 +3340,11 @@
           <t>01:35:51.388</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4712,6 +4727,11 @@
           <t>02:09:21.972</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>153408</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6209,6 +6229,11 @@
           <t>02:02:43.613</t>
         </is>
       </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7265,6 +7290,11 @@
           <t>01:33:39.263</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>54525</t>
@@ -7476,6 +7506,11 @@
           <t>54660</t>
         </is>
       </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>69453</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7610,6 +7645,11 @@
           <t>01:37:14.513</t>
         </is>
       </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>57977</t>
+        </is>
+      </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>57980</t>
@@ -8604,6 +8644,11 @@
           <t>01:26:35.752</t>
         </is>
       </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>42352</t>
+        </is>
+      </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>58793</t>
@@ -10430,6 +10475,11 @@
           <t>02:25:04.259</t>
         </is>
       </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>53061</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10982,6 +11032,11 @@
           <t>02:09:52.506</t>
         </is>
       </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11508,6 +11563,11 @@
           <t>02:27:56.026</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>61241</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12224,6 +12284,11 @@
           <t>02:14:10.609</t>
         </is>
       </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -14015,6 +14080,11 @@
           <t>02:01:00.649</t>
         </is>
       </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>57971</t>
+        </is>
+      </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>49438</t>
@@ -14406,6 +14476,11 @@
       <c r="L213" t="n">
         <v>234</v>
       </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>42352</t>
+        </is>
+      </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>58793</t>
@@ -14694,6 +14769,11 @@
           <t>02:01:44.737</t>
         </is>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -14956,6 +15036,11 @@
       <c r="L221" t="n">
         <v>254</v>
       </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>65954</t>
+        </is>
+      </c>
       <c r="X221" t="inlineStr">
         <is>
           <t>DNF</t>
@@ -15371,6 +15456,11 @@
           <t>02:03:26.251</t>
         </is>
       </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>49664</t>
@@ -15721,6 +15811,11 @@
           <t>02:10:08.051</t>
         </is>
       </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -15781,6 +15876,11 @@
       <c r="P233" t="inlineStr">
         <is>
           <t>02:10:18.735</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>47481</t>
         </is>
       </c>
       <c r="S233" t="inlineStr">
@@ -16532,7 +16632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20077,6 +20177,314 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>47481</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CAFFA</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>49618</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Mads Brandt</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>PEDERSEN</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>49654</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Levente</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BALLA</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>49663</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Adrian</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>BOROS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>49762</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Emil</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>TORSTENSSON</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>53061</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>MCLAIN</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>57971</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>FIGUERAS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>57977</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Pelayo</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>ROZA</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>58775</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Nuno</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>BARROS</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>61241</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>STAUBACH</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>65954</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Doug</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>ELLERY</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>69453</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Karl Find</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>HANSEN</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>98873</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Jon</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>MORENO BENITO</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>153408</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>COOK</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/OklahomaCity_2014_MAR/OklahomaCity_2014_MAR_Results.xlsx
+++ b/events/OklahomaCity_2014_MAR/OklahomaCity_2014_MAR_Results.xlsx
@@ -7094,6 +7094,11 @@
           <t>56154</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>94098</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -16632,7 +16637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20485,6 +20490,28 @@
         </is>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>94098</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Jean</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>VAN DER WESTHUIZEN</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
